--- a/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
+++ b/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
@@ -181,6 +181,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <sz val="11"/>

--- a/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
+++ b/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
@@ -4,6 +4,7 @@
   <sheets>
     <sheet name="Kitchen Sink Grid" sheetId="1" r:id="rId1"/>
     <sheet name="RTL Review" sheetId="2" r:id="rId2"/>
+    <sheet name="Filtered Review" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -1396,4 +1397,376 @@
     <mergeCell ref="M4:M6"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="30"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="29" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="32" customWidth="1"/>
+    <col min="12" max="12" width="42" customWidth="1"/>
+    <col min="13" max="13" width="27" customWidth="1"/>
+  </cols>
+  <autoFilter ref="A1:M10"/>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="4">
+        <v>8</v>
+      </c>
+      <c r="H2" s="5">
+        <v>1450</v>
+      </c>
+      <c r="I2" s="6">
+        <v>11600</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="9">
+        <v>45719.395833333336</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="4">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>950</v>
+      </c>
+      <c r="I3" s="10">
+        <v>950</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="4">
+        <v>24</v>
+      </c>
+      <c r="H4" s="5">
+        <v>79</v>
+      </c>
+      <c r="I4" s="6">
+        <v>1896</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="9">
+        <v>45723.395833333336</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="4">
+        <v>2</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1250</v>
+      </c>
+      <c r="I5" s="6">
+        <v>2500</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="8"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>600</v>
+      </c>
+      <c r="I6" s="10">
+        <v>600</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="9"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="4">
+        <v>5</v>
+      </c>
+      <c r="H7" s="5">
+        <v>39</v>
+      </c>
+      <c r="I7" s="6">
+        <v>195</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7" s="9">
+        <v>45728.395833333336</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="4">
+        <v>14</v>
+      </c>
+      <c r="H8" s="5">
+        <v>520</v>
+      </c>
+      <c r="I8" s="6">
+        <v>7280</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8" s="9">
+        <v>45734.395833333336</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="4">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5">
+        <v>2100</v>
+      </c>
+      <c r="I9" s="6">
+        <v>4200</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="9"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="12">
+        <v>4</v>
+      </c>
+      <c r="G10" s="12">
+        <v>57</v>
+      </c>
+      <c r="I10" s="13">
+        <v>29221</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="L4:L6"/>
+    <mergeCell ref="M4:M6"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:M9"/>
+  </mergeCells>
+</worksheet>
 </file>
--- a/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
+++ b/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
@@ -1401,24 +1401,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="32" customWidth="1"/>
-    <col min="12" max="12" width="42" customWidth="1"/>
-    <col min="13" max="13" width="27" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="42" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
   </cols>
-  <autoFilter ref="A1:M10"/>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
@@ -1434,30 +1427,12 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1474,299 +1449,91 @@
       <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="4">
-        <v>8</v>
-      </c>
-      <c r="H2" s="5">
-        <v>1450</v>
-      </c>
-      <c r="I2" s="6">
-        <v>11600</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="9">
+      <c r="G2" s="9">
         <v>45719.395833333336</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>950</v>
-      </c>
-      <c r="I3" s="10">
-        <v>950</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="9"/>
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="9">
+        <v>45723.395833333336</v>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="4">
-        <v>24</v>
-      </c>
-      <c r="H4" s="5">
-        <v>79</v>
-      </c>
-      <c r="I4" s="6">
-        <v>1896</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="9">
-        <v>45723.395833333336</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="4">
-        <v>2</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1250</v>
-      </c>
-      <c r="I5" s="6">
-        <v>2500</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="8"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="9"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="4">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5">
-        <v>600</v>
-      </c>
-      <c r="I6" s="10">
-        <v>600</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="9"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="4">
-        <v>5</v>
-      </c>
-      <c r="H7" s="5">
-        <v>39</v>
-      </c>
-      <c r="I7" s="6">
-        <v>195</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M7" s="9">
+      <c r="G4" s="9">
         <v>45728.395833333336</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="2" t="s">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="4">
-        <v>14</v>
-      </c>
-      <c r="H8" s="5">
-        <v>520</v>
-      </c>
-      <c r="I8" s="6">
-        <v>7280</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="9">
+      <c r="G5" s="9">
         <v>45734.395833333336</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="4">
-        <v>2</v>
-      </c>
-      <c r="H9" s="5">
-        <v>2100</v>
-      </c>
-      <c r="I9" s="6">
-        <v>4200</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="9"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="12">
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="12">
         <v>4</v>
       </c>
-      <c r="G10" s="12">
-        <v>57</v>
-      </c>
-      <c r="I10" s="13">
-        <v>29221</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="L4:L6"/>
-    <mergeCell ref="M4:M6"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="M8:M9"/>
-  </mergeCells>
+  <autoFilter ref="A1:G6"/>
 </worksheet>
 </file>
--- a/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
+++ b/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
@@ -5,12 +5,13 @@
     <sheet name="Kitchen Sink Grid" sheetId="1" r:id="rId1"/>
     <sheet name="RTL Review" sheetId="2" r:id="rId2"/>
     <sheet name="Filtered Review" sheetId="3" r:id="rId3"/>
+    <sheet name="Formula Summaries" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Order</t>
   </si>
@@ -176,6 +177,12 @@
   </si>
   <si>
     <t>Network gateway</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -1536,4 +1543,84 @@
   </sheetData>
   <autoFilter ref="A1:G6"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="30"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="5">
+        <v>12550</v>
+      </c>
+      <c r="C2" s="9">
+        <v>45719.395833333336</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="5">
+        <v>4996</v>
+      </c>
+      <c r="C3" s="9">
+        <v>45723.395833333336</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5">
+        <v>195</v>
+      </c>
+      <c r="C4" s="9">
+        <v>45728.395833333336</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="5">
+        <v>11480</v>
+      </c>
+      <c r="C5" s="9">
+        <v>45734.395833333336</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="13">
+        <f>SUM(B2:B5)</f>
+      </c>
+      <c r="C6" s="12">
+        <f>MAX(C2:C5)</f>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
+++ b/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
@@ -291,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -331,6 +331,9 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1617,7 +1620,7 @@
       <c r="B6" s="13">
         <f>SUM(B2:B5)</f>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="14">
         <f>MAX(C2:C5)</f>
       </c>
     </row>

--- a/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
+++ b/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
@@ -6,12 +6,13 @@
     <sheet name="RTL Review" sheetId="2" r:id="rId2"/>
     <sheet name="Filtered Review" sheetId="3" r:id="rId3"/>
     <sheet name="Formula Summaries" sheetId="4" r:id="rId4"/>
+    <sheet name="Formula Columns" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Order</t>
   </si>
@@ -182,16 +183,48 @@
     <t>Amount</t>
   </si>
   <si>
+    <t>Items</t>
+  </si>
+  <si>
+    <t>Fulfilled %</t>
+  </si>
+  <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>AVERAGE / LATEST</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>Activated</t>
+  </si>
+  <si>
+    <t>Gross</t>
+  </si>
+  <si>
+    <t>Net</t>
+  </si>
+  <si>
+    <t>Utilization</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>Risk</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -291,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -332,8 +365,20 @@
     <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1550,12 +1595,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1566,6 +1613,12 @@
         <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1576,7 +1629,13 @@
       <c r="B2" s="5">
         <v>12550</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="4">
+        <v>2</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="9">
         <v>45719.395833333336</v>
       </c>
     </row>
@@ -1587,7 +1646,13 @@
       <c r="B3" s="5">
         <v>4996</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="4">
+        <v>3</v>
+      </c>
+      <c r="D3" s="14">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E3" s="9">
         <v>45723.395833333336</v>
       </c>
     </row>
@@ -1598,7 +1663,13 @@
       <c r="B4" s="5">
         <v>195</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="14">
+        <v>1</v>
+      </c>
+      <c r="E4" s="9">
         <v>45728.395833333336</v>
       </c>
     </row>
@@ -1609,19 +1680,235 @@
       <c r="B5" s="5">
         <v>11480</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="4">
+        <v>2</v>
+      </c>
+      <c r="D5" s="14">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9">
         <v>45734.395833333336</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B6" s="13">
-        <f>SUM(B2:B5)</f>
-      </c>
-      <c r="C6" s="14">
-        <f>MAX(C2:C5)</f>
+        <f>ROUND(SUM(B2:B5),2)</f>
+      </c>
+      <c r="C6" s="15">
+        <f>SUM(C2:C5)</f>
+      </c>
+      <c r="D6" s="16">
+        <f>ROUND(AVERAGE(D2:D5),4)</f>
+      </c>
+      <c r="E6" s="12"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="13">
+        <f>ROUND(AVERAGE(B2:B5),2)</f>
+      </c>
+      <c r="C7" s="15">
+        <f>AVERAGE(C2:C5)</f>
+      </c>
+      <c r="D7" s="16">
+        <f>MAX(MAX(D2:D5),0)</f>
+      </c>
+      <c r="E7" s="17">
+        <f>MAX(MAX(E2:E5),0)</f>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="30"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4">
+        <v>9</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1200</v>
+      </c>
+      <c r="D2" s="18">
+        <v>0.18</v>
+      </c>
+      <c r="E2" s="4">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5">
+        <f>ROUND((B2*C2),2)</f>
+      </c>
+      <c r="G2" s="5">
+        <f>ROUND((F2*(1-D2)),2)</f>
+      </c>
+      <c r="H2" s="14">
+        <f>IF((B2&gt;0),ROUND((E2/B2),4),0)</f>
+      </c>
+      <c r="I2" s="2">
+        <f>IF(OR((G2&gt;=5000),(H2&gt;=0.85)),"HIGH",IF((D2&gt;=0.15),"WATCH","STANDARD"))</f>
+      </c>
+      <c r="J2" s="2">
+        <f>IF(OR((I2="WATCH"),(H2&lt;0.5)),"REVIEW","OK")</f>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="4">
+        <v>27</v>
+      </c>
+      <c r="C3" s="5">
+        <v>643</v>
+      </c>
+      <c r="D3" s="18">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="4">
+        <v>26</v>
+      </c>
+      <c r="F3" s="5">
+        <f>ROUND((B3*C3),2)</f>
+      </c>
+      <c r="G3" s="5">
+        <f>ROUND((F3*(1-D3)),2)</f>
+      </c>
+      <c r="H3" s="14">
+        <f>IF((B3&gt;0),ROUND((E3/B3),4),0)</f>
+      </c>
+      <c r="I3" s="2">
+        <f>IF(OR((G3&gt;=5000),(H3&gt;=0.85)),"HIGH",IF((D3&gt;=0.15),"WATCH","STANDARD"))</f>
+      </c>
+      <c r="J3" s="2">
+        <f>IF(OR((I3="WATCH"),(H3&lt;0.5)),"REVIEW","OK")</f>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5">
+        <v>39</v>
+      </c>
+      <c r="D4" s="18">
+        <v>0.03</v>
+      </c>
+      <c r="E4" s="4">
+        <v>5</v>
+      </c>
+      <c r="F4" s="5">
+        <f>ROUND((B4*C4),2)</f>
+      </c>
+      <c r="G4" s="5">
+        <f>ROUND((F4*(1-D4)),2)</f>
+      </c>
+      <c r="H4" s="14">
+        <f>IF((B4&gt;0),ROUND((E4/B4),4),0)</f>
+      </c>
+      <c r="I4" s="2">
+        <f>IF(OR((G4&gt;=5000),(H4&gt;=0.85)),"HIGH",IF((D4&gt;=0.15),"WATCH","STANDARD"))</f>
+      </c>
+      <c r="J4" s="2">
+        <f>IF(OR((I4="WATCH"),(H4&lt;0.5)),"REVIEW","OK")</f>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="4">
+        <v>16</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1310</v>
+      </c>
+      <c r="D5" s="18">
+        <v>0.18</v>
+      </c>
+      <c r="E5" s="4">
+        <v>16</v>
+      </c>
+      <c r="F5" s="5">
+        <f>ROUND((B5*C5),2)</f>
+      </c>
+      <c r="G5" s="5">
+        <f>ROUND((F5*(1-D5)),2)</f>
+      </c>
+      <c r="H5" s="14">
+        <f>IF((B5&gt;0),ROUND((E5/B5),4),0)</f>
+      </c>
+      <c r="I5" s="2">
+        <f>IF(OR((G5&gt;=5000),(H5&gt;=0.85)),"HIGH",IF((D5&gt;=0.15),"WATCH","STANDARD"))</f>
+      </c>
+      <c r="J5" s="2">
+        <f>IF(OR((I5="WATCH"),(H5&lt;0.5)),"REVIEW","OK")</f>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="F6" s="13">
+        <f>ROUND(SUM(F2:F5),2)</f>
+      </c>
+      <c r="G6" s="13">
+        <f>ROUND(SUM(G2:G5),2)</f>
       </c>
     </row>
   </sheetData>

--- a/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
+++ b/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Filtered Review" sheetId="3" r:id="rId3"/>
     <sheet name="Formula Summaries" sheetId="4" r:id="rId4"/>
     <sheet name="Formula Columns" sheetId="5" r:id="rId5"/>
+    <sheet name="Native Excel Table" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -324,7 +325,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -380,11 +381,30 @@
     <xf numFmtId="167" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="KitchenSinkOrders" displayName="KitchenSinkOrders" ref="A1:G6" totalsRowCount="1" headerRowCount="1">
+  <autoFilter ref="A1:G5"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Order" totalsRowLabel="TOTAL"/>
+    <tableColumn id="2" name="Customer"/>
+    <tableColumn id="3" name="Account"/>
+    <tableColumn id="4" name="Email"/>
+    <tableColumn id="5" name="Items"/>
+    <tableColumn id="6" name="Line Total" totalsRowFunction="sum"/>
+    <tableColumn id="7" name="Created" totalsRowFunction="max"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1913,4 +1933,151 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="30"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="29" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="4">
+        <v>2</v>
+      </c>
+      <c r="F2" s="5">
+        <v>12550</v>
+      </c>
+      <c r="G2" s="9">
+        <v>45719.395833333336</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="4">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5">
+        <v>4996</v>
+      </c>
+      <c r="G3" s="9">
+        <v>45723.395833333336</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>195</v>
+      </c>
+      <c r="G4" s="9">
+        <v>45728.395833333336</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2</v>
+      </c>
+      <c r="F5" s="5">
+        <v>11480</v>
+      </c>
+      <c r="G5" s="9">
+        <v>45734.395833333336</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="13">
+        <f>SUBTOTAL(109,[Line Total])</f>
+      </c>
+      <c r="G6" s="17">
+        <f>SUBTOTAL(104,[Created])</f>
+      </c>
+    </row>
+  </sheetData>
+  <tableParts count="1">
+    <tablePart r:id="rIdTable1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
+++ b/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
@@ -8,12 +8,13 @@
     <sheet name="Formula Summaries" sheetId="4" r:id="rId4"/>
     <sheet name="Formula Columns" sheetId="5" r:id="rId5"/>
     <sheet name="Native Excel Table" sheetId="6" r:id="rId6"/>
+    <sheet name="Grouped Formula Scope" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>Order</t>
   </si>
@@ -215,6 +216,36 @@
   </si>
   <si>
     <t>Risk</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>AMER Amount</t>
+  </si>
+  <si>
+    <t>APAC Amount</t>
+  </si>
+  <si>
+    <t>EMEA Amount</t>
+  </si>
+  <si>
+    <t>Regional Total</t>
+  </si>
+  <si>
+    <t>Regional Avg</t>
+  </si>
+  <si>
+    <t>EMEA</t>
+  </si>
+  <si>
+    <t>AMER</t>
+  </si>
+  <si>
+    <t>APAC</t>
+  </si>
+  <si>
+    <t>AVERAGE</t>
   </si>
 </sst>
 </file>
@@ -407,6 +438,33 @@
 </table>
 </file>
 
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="KitchenSinkRegionalScope" displayName="KitchenSinkRegionalScope" ref="A1:H6" totalsRowCount="1" headerRowCount="1">
+  <autoFilter ref="A1:H5"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Customer" totalsRowLabel="AVERAGE"/>
+    <tableColumn id="2" name="Amount" totalsRowFunction="average"/>
+    <tableColumn id="3" name="Region"/>
+    <tableColumn id="4" name="AMER Amount">
+      <calculatedColumnFormula>IF((KitchenSinkRegionalScope[@[Region]]="AMER"),KitchenSinkRegionalScope[@[Amount]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" name="APAC Amount">
+      <calculatedColumnFormula>IF((KitchenSinkRegionalScope[@[Region]]="APAC"),KitchenSinkRegionalScope[@[Amount]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" name="EMEA Amount">
+      <calculatedColumnFormula>IF((KitchenSinkRegionalScope[@[Region]]="EMEA"),KitchenSinkRegionalScope[@[Amount]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" name="Regional Total" totalsRowFunction="sum">
+      <calculatedColumnFormula>SUM(KitchenSinkRegionalScope[@[AMER Amount]:[EMEA Amount]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" name="Regional Avg" totalsRowFunction="average">
+      <calculatedColumnFormula>ROUND(AVERAGE(KitchenSinkRegionalScope[@[AMER Amount]:[EMEA Amount]]),2)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:W22"/>
@@ -2080,4 +2138,170 @@
     <tablePart r:id="rIdTable1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="30"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="5">
+        <v>12550</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="5">
+        <f>IF(([@[Region]]="AMER"),[@[Amount]],0)</f>
+      </c>
+      <c r="E2" s="5">
+        <f>IF(([@[Region]]="APAC"),[@[Amount]],0)</f>
+      </c>
+      <c r="F2" s="5">
+        <f>IF(([@[Region]]="EMEA"),[@[Amount]],0)</f>
+      </c>
+      <c r="G2" s="5">
+        <f>SUM([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]])</f>
+      </c>
+      <c r="H2" s="5">
+        <f>ROUND(AVERAGE([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]]),2)</f>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="5">
+        <v>4996</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="5">
+        <f>IF(([@[Region]]="AMER"),[@[Amount]],0)</f>
+      </c>
+      <c r="E3" s="5">
+        <f>IF(([@[Region]]="APAC"),[@[Amount]],0)</f>
+      </c>
+      <c r="F3" s="5">
+        <f>IF(([@[Region]]="EMEA"),[@[Amount]],0)</f>
+      </c>
+      <c r="G3" s="5">
+        <f>SUM([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]])</f>
+      </c>
+      <c r="H3" s="5">
+        <f>ROUND(AVERAGE([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]]),2)</f>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5">
+        <v>195</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="5">
+        <f>IF(([@[Region]]="AMER"),[@[Amount]],0)</f>
+      </c>
+      <c r="E4" s="5">
+        <f>IF(([@[Region]]="APAC"),[@[Amount]],0)</f>
+      </c>
+      <c r="F4" s="5">
+        <f>IF(([@[Region]]="EMEA"),[@[Amount]],0)</f>
+      </c>
+      <c r="G4" s="5">
+        <f>SUM([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]])</f>
+      </c>
+      <c r="H4" s="5">
+        <f>ROUND(AVERAGE([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]]),2)</f>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="5">
+        <v>11480</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="5">
+        <f>IF(([@[Region]]="AMER"),[@[Amount]],0)</f>
+      </c>
+      <c r="E5" s="5">
+        <f>IF(([@[Region]]="APAC"),[@[Amount]],0)</f>
+      </c>
+      <c r="F5" s="5">
+        <f>IF(([@[Region]]="EMEA"),[@[Amount]],0)</f>
+      </c>
+      <c r="G5" s="5">
+        <f>SUM([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]])</f>
+      </c>
+      <c r="H5" s="5">
+        <f>ROUND(AVERAGE([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]]),2)</f>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="13">
+        <f>SUBTOTAL(101,[Amount])</f>
+      </c>
+      <c r="G6" s="13">
+        <f>SUBTOTAL(109,[Regional Total])</f>
+      </c>
+      <c r="H6" s="13">
+        <f>SUBTOTAL(101,[Regional Avg])</f>
+      </c>
+    </row>
+  </sheetData>
+  <tableParts count="1">
+    <tablePart r:id="rIdTable1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
+++ b/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
@@ -8,13 +8,12 @@
     <sheet name="Formula Summaries" sheetId="4" r:id="rId4"/>
     <sheet name="Formula Columns" sheetId="5" r:id="rId5"/>
     <sheet name="Native Excel Table" sheetId="6" r:id="rId6"/>
-    <sheet name="Grouped Formula Scope" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Order</t>
   </si>
@@ -216,36 +215,6 @@
   </si>
   <si>
     <t>Risk</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>AMER Amount</t>
-  </si>
-  <si>
-    <t>APAC Amount</t>
-  </si>
-  <si>
-    <t>EMEA Amount</t>
-  </si>
-  <si>
-    <t>Regional Total</t>
-  </si>
-  <si>
-    <t>Regional Avg</t>
-  </si>
-  <si>
-    <t>EMEA</t>
-  </si>
-  <si>
-    <t>AMER</t>
-  </si>
-  <si>
-    <t>APAC</t>
-  </si>
-  <si>
-    <t>AVERAGE</t>
   </si>
 </sst>
 </file>
@@ -419,6 +388,61 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF166534"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1D4ED8"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9A3412"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEDD5"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thick">
+          <color rgb="FFEA580C"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <diagonal/>
+      </border>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -435,33 +459,6 @@
     <tableColumn id="7" name="Created" totalsRowFunction="max"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="KitchenSinkRegionalScope" displayName="KitchenSinkRegionalScope" ref="A1:H6" totalsRowCount="1" headerRowCount="1">
-  <autoFilter ref="A1:H5"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="Customer" totalsRowLabel="AVERAGE"/>
-    <tableColumn id="2" name="Amount" totalsRowFunction="average"/>
-    <tableColumn id="3" name="Region"/>
-    <tableColumn id="4" name="AMER Amount">
-      <calculatedColumnFormula>IF((KitchenSinkRegionalScope[@[Region]]="AMER"),KitchenSinkRegionalScope[@[Amount]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" name="APAC Amount">
-      <calculatedColumnFormula>IF((KitchenSinkRegionalScope[@[Region]]="APAC"),KitchenSinkRegionalScope[@[Amount]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" name="EMEA Amount">
-      <calculatedColumnFormula>IF((KitchenSinkRegionalScope[@[Region]]="EMEA"),KitchenSinkRegionalScope[@[Amount]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" name="Regional Total" totalsRowFunction="sum">
-      <calculatedColumnFormula>SUM(KitchenSinkRegionalScope[@[AMER Amount]:[EMEA Amount]])</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" name="Regional Avg" totalsRowFunction="average">
-      <calculatedColumnFormula>ROUND(AVERAGE(KitchenSinkRegionalScope[@[AMER Amount]:[EMEA Amount]]),2)</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1801,6 +1798,32 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>(B6&gt;=40000)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>(D6&lt;0.6)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>(D6&gt;=0.85)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="expression" dxfId="1" priority="4">
+      <formula>(B7&lt;5000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="5">
+      <formula>(B7&gt;=8000)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7">
+    <cfRule type="expression" dxfId="2" priority="6">
+      <formula>(D7&gt;=0.95)</formula>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>
 
@@ -1990,6 +2013,22 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="G2:G5">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>($G2&lt;1000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>AND(($G2&gt;=5000),(H2&gt;=0.85))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J5">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>($J2="REVIEW")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>($J2="OK")</formula>
+    </cfRule>
+  </conditionalFormatting>
 </worksheet>
 </file>
 
@@ -2138,170 +2177,4 @@
     <tablePart r:id="rIdTable1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="30"/>
-  <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="5">
-        <v>12550</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="5">
-        <f>IF(([@[Region]]="AMER"),[@[Amount]],0)</f>
-      </c>
-      <c r="E2" s="5">
-        <f>IF(([@[Region]]="APAC"),[@[Amount]],0)</f>
-      </c>
-      <c r="F2" s="5">
-        <f>IF(([@[Region]]="EMEA"),[@[Amount]],0)</f>
-      </c>
-      <c r="G2" s="5">
-        <f>SUM([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]])</f>
-      </c>
-      <c r="H2" s="5">
-        <f>ROUND(AVERAGE([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]]),2)</f>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="5">
-        <v>4996</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="5">
-        <f>IF(([@[Region]]="AMER"),[@[Amount]],0)</f>
-      </c>
-      <c r="E3" s="5">
-        <f>IF(([@[Region]]="APAC"),[@[Amount]],0)</f>
-      </c>
-      <c r="F3" s="5">
-        <f>IF(([@[Region]]="EMEA"),[@[Amount]],0)</f>
-      </c>
-      <c r="G3" s="5">
-        <f>SUM([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]])</f>
-      </c>
-      <c r="H3" s="5">
-        <f>ROUND(AVERAGE([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]]),2)</f>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="5">
-        <v>195</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" s="5">
-        <f>IF(([@[Region]]="AMER"),[@[Amount]],0)</f>
-      </c>
-      <c r="E4" s="5">
-        <f>IF(([@[Region]]="APAC"),[@[Amount]],0)</f>
-      </c>
-      <c r="F4" s="5">
-        <f>IF(([@[Region]]="EMEA"),[@[Amount]],0)</f>
-      </c>
-      <c r="G4" s="5">
-        <f>SUM([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]])</f>
-      </c>
-      <c r="H4" s="5">
-        <f>ROUND(AVERAGE([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]]),2)</f>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="5">
-        <v>11480</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="5">
-        <f>IF(([@[Region]]="AMER"),[@[Amount]],0)</f>
-      </c>
-      <c r="E5" s="5">
-        <f>IF(([@[Region]]="APAC"),[@[Amount]],0)</f>
-      </c>
-      <c r="F5" s="5">
-        <f>IF(([@[Region]]="EMEA"),[@[Amount]],0)</f>
-      </c>
-      <c r="G5" s="5">
-        <f>SUM([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]])</f>
-      </c>
-      <c r="H5" s="5">
-        <f>ROUND(AVERAGE([@[AMER Amount]],[@[APAC Amount]],[@[EMEA Amount]]),2)</f>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="13">
-        <f>SUBTOTAL(101,[Amount])</f>
-      </c>
-      <c r="G6" s="13">
-        <f>SUBTOTAL(109,[Regional Total])</f>
-      </c>
-      <c r="H6" s="13">
-        <f>SUBTOTAL(101,[Regional Avg])</f>
-      </c>
-    </row>
-  </sheetData>
-  <tableParts count="1">
-    <tablePart r:id="rIdTable1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
+++ b/packages/typed-xlsx/examples/kitchen-sink-buffered.xlsx
@@ -1,19 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookProtection lockStructure="1" workbookPassword="B522"/>
   <sheets>
     <sheet name="Kitchen Sink Grid" sheetId="1" r:id="rId1"/>
     <sheet name="RTL Review" sheetId="2" r:id="rId2"/>
     <sheet name="Filtered Review" sheetId="3" r:id="rId3"/>
     <sheet name="Formula Summaries" sheetId="4" r:id="rId4"/>
     <sheet name="Formula Columns" sheetId="5" r:id="rId5"/>
-    <sheet name="Native Excel Table" sheetId="6" r:id="rId6"/>
+    <sheet name="Validation" sheetId="6" r:id="rId6"/>
+    <sheet name="Protected Input" sheetId="7" r:id="rId7"/>
+    <sheet name="Hyperlinks" sheetId="8" r:id="rId8"/>
+    <sheet name="Native Excel Table" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Order</t>
   </si>
@@ -215,19 +219,44 @@
   </si>
   <si>
     <t>Risk</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>archived</t>
+  </si>
+  <si>
+    <t>Requested Budget</t>
+  </si>
+  <si>
+    <t>Approved Budget</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0%"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -255,6 +284,14 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF7C3AED"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0563C1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -325,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -380,6 +417,27 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2034,6 +2092,250 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="30"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="5">
+        <v>12550</v>
+      </c>
+      <c r="D2" s="19">
+        <v>45719.395833333336</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="5">
+        <v>4996</v>
+      </c>
+      <c r="D3" s="19">
+        <v>45723.395833333336</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="5">
+        <v>195</v>
+      </c>
+      <c r="D4" s="19">
+        <v>45728.395833333336</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="5">
+        <v>11480</v>
+      </c>
+      <c r="D5" s="19">
+        <v>45734.395833333336</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="C6" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="C7" s="13">
+        <f>SUM(C2:C5)</f>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="B2:B5" type="list" showInputMessage="1" promptTitle="Allowed values" prompt="Choose draft, active, or archived" showErrorMessage="1" errorTitle="Invalid status" error="Use one of the allowed workflow states" errorStyle="stop">
+      <formula1>"draft,active,archived"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C5" type="whole" operator="between" allowBlank="1" showErrorMessage="1" errorStyle="stop">
+      <formula1>100</formula1>
+      <formula2>100000</formula2>
+    </dataValidation>
+    <dataValidation sqref="D2:D5" type="date" operator="greaterThanOrEqual" showErrorMessage="1" errorStyle="stop">
+      <formula1>45658</formula1>
+    </dataValidation>
+  </dataValidations>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="30"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="21">
+        <v>12550</v>
+      </c>
+      <c r="C2" s="22">
+        <f>ROUND((B2*0.9),0)</f>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="21">
+        <v>4996</v>
+      </c>
+      <c r="C3" s="22">
+        <f>ROUND((B3*0.9),0)</f>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="21">
+        <v>195</v>
+      </c>
+      <c r="C4" s="22">
+        <f>ROUND((B4*0.9),0)</f>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="21">
+        <v>11480</v>
+      </c>
+      <c r="C5" s="22">
+        <f>ROUND((B5*0.9),0)</f>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" password="A456" selectLockedCells="1"/>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B5" type="whole" operator="between" showErrorMessage="1" errorTitle="Invalid budget" error="Use a whole number between 1,000 and 50,000" errorStyle="stop">
+      <formula1>1000</formula1>
+      <formula2>50000</formula2>
+    </dataValidation>
+  </dataValidations>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="30"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" tooltip="Open customer record" r:id="rIdHyperlink1"/>
+    <hyperlink ref="B2" tooltip="Send email" r:id="rIdHyperlink2"/>
+    <hyperlink ref="B3" tooltip="Send email" r:id="rIdHyperlink3"/>
+    <hyperlink ref="A4" tooltip="Open customer record" r:id="rIdHyperlink4"/>
+    <hyperlink ref="B4" tooltip="Send email" r:id="rIdHyperlink5"/>
+    <hyperlink ref="B5" tooltip="Send email" r:id="rIdHyperlink6"/>
+  </hyperlinks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
@@ -2047,25 +2349,25 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="25" t="s">
         <v>12</v>
       </c>
     </row>
